--- a/artfynd/A 14554-2026 artfynd.xlsx
+++ b/artfynd/A 14554-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ122"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18034,47 +18034,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>94277631</v>
+        <v>137259216</v>
       </c>
       <c r="B122" t="n">
-        <v>43438</v>
+        <v>43474</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>101298</v>
+        <v>100942</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -18086,13 +18084,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614564</v>
+        <v>614594</v>
       </c>
       <c r="R122" t="n">
-        <v>6724484</v>
+        <v>6724444</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -18116,27 +18114,27 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>100% sol, ingen molnighet, västlig vind, 5 m/s, 18°.</t>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -18145,23 +18143,841 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259216</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>137259230</v>
+      </c>
+      <c r="B123" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>614602</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6724406</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259230</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>137259232</v>
+      </c>
+      <c r="B124" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>614608</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6724418</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259232</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>137259233</v>
+      </c>
+      <c r="B125" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>614587</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6724457</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259233</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>137259234</v>
+      </c>
+      <c r="B126" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>614556</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6724494</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259234</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>137259235</v>
+      </c>
+      <c r="B127" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>614496</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6724574</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>18 grader varmt, halv-klart, 4-5 m/s, västlig vind, 60% sol.</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259235</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>94277631</v>
+      </c>
+      <c r="B128" t="n">
+        <v>43438</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>101298</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Melitaea diamina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skogmur, Gstr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>614564</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6724484</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>100% sol, ingen molnighet, västlig vind, 5 m/s, 18°.</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
           <t>Gustav Wikström</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AX128" t="inlineStr">
         <is>
           <t>Gustav Wikström, Göran Vesslén</t>
         </is>
       </c>
-      <c r="AY122" t="inlineStr"/>
-      <c r="AZ122" t="inlineStr">
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/94277631</t>
         </is>
@@ -18290,6 +19106,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14554-2026 artfynd.xlsx
+++ b/artfynd/A 14554-2026 artfynd.xlsx
@@ -18037,7 +18037,7 @@
         <v>137259216</v>
       </c>
       <c r="B122" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>137259230</v>
       </c>
       <c r="B123" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>137259232</v>
       </c>
       <c r="B124" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>137259233</v>
       </c>
       <c r="B125" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>137259234</v>
       </c>
       <c r="B126" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>137259235</v>
       </c>
       <c r="B127" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 14554-2026 artfynd.xlsx
+++ b/artfynd/A 14554-2026 artfynd.xlsx
@@ -18037,7 +18037,7 @@
         <v>137259216</v>
       </c>
       <c r="B122" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>137259230</v>
       </c>
       <c r="B123" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>137259232</v>
       </c>
       <c r="B124" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>137259233</v>
       </c>
       <c r="B125" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>137259234</v>
       </c>
       <c r="B126" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>137259235</v>
       </c>
       <c r="B127" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
